--- a/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2EB5E49-D86D-4916-935E-D593183BDFD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9CE8576-3FCA-4C74-8FCA-24685395EB0A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{790D4156-54AC-4A12-9BC4-420E3D160A06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2B53C9A-52F3-4516-B7C9-34C7ED0301EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0426204E-1B6A-4DF4-831E-E873D7AF8354}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAC3BB1-58A6-4348-9332-42F9D681562B}"/>
 </file>